--- a/AAII_Financials/Quarterly/INVZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INVZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
   <si>
     <t>INVZ</t>
   </si>
@@ -656,123 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
-        <v>45473</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
@@ -782,88 +782,91 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E8" s="3">
         <v>12700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>17400</v>
+      </c>
+      <c r="I8" s="3">
         <v>6000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4500</v>
       </c>
-      <c r="I8" s="3">
-        <v>6700</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>900</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1800</v>
       </c>
       <c r="S8" s="3">
         <v>1800</v>
       </c>
       <c r="T8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U8" s="3">
         <v>1700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3">
         <v>1800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>800</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -871,86 +874,89 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E9" s="3">
         <v>10600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I9" s="3">
         <v>5500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>4700</v>
       </c>
-      <c r="I9" s="3">
-        <v>6900</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2100</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,86 +966,89 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-200</v>
       </c>
-      <c r="I10" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-2300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-3200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-2300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-2200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-3900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-3700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-3100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-1100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-800</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3">
         <v>500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1049,8 +1058,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1082,86 +1094,87 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E12" s="3">
         <v>16100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>14800</v>
+      </c>
+      <c r="I12" s="3">
         <v>13500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>19700</v>
       </c>
-      <c r="I12" s="3">
-        <v>16800</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>32100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>57000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>14700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>15700</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,8 +1184,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1260,17 +1276,20 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1286,12 +1305,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1301,8 +1320,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1349,8 +1368,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1358,41 +1380,41 @@
         <v>1300</v>
       </c>
       <c r="E15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="M15" s="3">
         <v>2000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="N15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O15" s="3">
         <v>1500</v>
       </c>
-      <c r="L15" s="3">
-        <v>2000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2300</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1438,8 +1460,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1468,8 +1493,9 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1477,77 +1503,77 @@
         <v>33600</v>
       </c>
       <c r="E17" s="3">
+        <v>33600</v>
+      </c>
+      <c r="F17" s="3">
         <v>31100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>31400</v>
+      </c>
+      <c r="I17" s="3">
         <v>25300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>30700</v>
       </c>
-      <c r="I17" s="3">
-        <v>30200</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>37000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>72800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>72600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>20200</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1557,86 +1583,89 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-19200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-26200</v>
       </c>
-      <c r="I18" s="3">
-        <v>-23500</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-30000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-34900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-30600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-31700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-35300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-30100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-71800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-20500</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,8 +1675,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1679,86 +1711,87 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2500</v>
-      </c>
-      <c r="S20" s="3">
-        <v>1500</v>
       </c>
       <c r="T20" s="3">
         <v>1500</v>
       </c>
       <c r="U20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V20" s="3">
         <v>3700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1768,86 +1801,89 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-18200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-26000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-71800</v>
+      </c>
+      <c r="X21" s="3">
         <v>-20000</v>
       </c>
-      <c r="J21" s="3">
-        <v>-20100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-31800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-20100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-27700</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-32000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-35800</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-32600</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-32400</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-26000</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-28100</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-31800</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-25700</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-71800</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1857,23 +1893,26 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>-1900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1900</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1898,8 +1937,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1946,86 +1985,89 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-18600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-24800</v>
       </c>
-      <c r="I23" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-34400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-34200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-30200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-33800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-26400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-72500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-20600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-81300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2035,25 +2077,28 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -2074,14 +2119,14 @@
         <v>100</v>
       </c>
       <c r="O24" s="3">
+        <v>100</v>
+      </c>
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2089,32 +2134,32 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2124,8 +2169,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2213,86 +2261,89 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-18600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-24900</v>
       </c>
-      <c r="I26" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-34300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-28100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-30200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-33900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-26400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-72500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-20700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-81500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,86 +2353,89 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-18600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-24900</v>
       </c>
-      <c r="I27" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-30500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-28100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-30200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-33900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-26400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-72500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-20700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-81500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,8 +2445,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2480,8 +2537,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2569,8 +2629,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2658,8 +2721,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2747,86 +2813,89 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3">
+        <v>600</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-1500</v>
       </c>
       <c r="T32" s="3">
         <v>-1500</v>
       </c>
       <c r="U32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="V32" s="3">
         <v>-3700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,86 +2905,89 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-18600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-24900</v>
       </c>
-      <c r="I33" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-30500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-28100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-30200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-33900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-26400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-72500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-20700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-81500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,8 +2997,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3014,86 +3089,89 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-18600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-24900</v>
       </c>
-      <c r="I35" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-30500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-28100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-30200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-33900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-26400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-72500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-20700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-81500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,91 +3181,94 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
-        <v>45473</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3197,8 +3278,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3230,8 +3314,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3263,71 +3348,72 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E41" s="3">
         <v>8600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I41" s="3">
         <v>25400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>27900</v>
       </c>
-      <c r="I41" s="3">
-        <v>24000</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>34300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>113400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>55700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>168100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>50300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>139600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>156400</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,65 +3438,68 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E42" s="3">
         <v>63500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>66500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>65800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I42" s="3">
         <v>42600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>59800</v>
       </c>
-      <c r="I42" s="3">
-        <v>81100</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>119100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>87300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>119100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>126500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>87300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>35200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>41700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>34600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>21900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>15200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>11600</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,8 +3512,8 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3441,70 +3530,73 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E43" s="3">
         <v>11200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
+        <v>17700</v>
+      </c>
+      <c r="I43" s="3">
         <v>6200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3500</v>
       </c>
-      <c r="I43" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>800</v>
-      </c>
-      <c r="R43" s="3">
-        <v>1100</v>
       </c>
       <c r="S43" s="3">
         <v>1100</v>
       </c>
       <c r="T43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U43" s="3">
         <v>500</v>
-      </c>
-      <c r="U43" s="3">
-        <v>600</v>
       </c>
       <c r="V43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>600</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
@@ -3521,8 +3613,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3530,71 +3622,74 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E44" s="3">
         <v>3300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I44" s="3">
         <v>1900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4200</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>4700</v>
       </c>
       <c r="R44" s="3">
         <v>4700</v>
       </c>
       <c r="S44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T44" s="3">
         <v>4600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3700</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3705,8 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -3619,71 +3714,74 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>5700</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>4100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>4100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>84200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>152600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>209700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>234400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>191000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>204800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3708,71 +3806,74 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E46" s="3">
         <v>90200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>102200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>100900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>108600</v>
+      </c>
+      <c r="I46" s="3">
         <v>82600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>94800</v>
       </c>
-      <c r="I46" s="3">
-        <v>114400</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>160500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>131100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>160500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>171500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>131100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>157800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>187600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>212200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>230500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>250200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>274400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>335800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>365500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,8 +3898,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3817,45 +3921,45 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>4800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>14500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>27300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>34100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>38300</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,14 +3972,14 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
+      <c r="AB47" s="3">
+        <v>0</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
@@ -3886,71 +3990,74 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E48" s="3">
         <v>44900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>47200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
+        <v>45800</v>
+      </c>
+      <c r="I48" s="3">
         <v>46600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>46800</v>
       </c>
-      <c r="I48" s="3">
-        <v>48500</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>51300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>57300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>58100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>57400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>54800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>48800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>42100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3966,8 +4073,8 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -3975,8 +4082,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4064,8 +4174,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4153,8 +4266,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4242,43 +4358,46 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E52" s="3">
         <v>3300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2800</v>
       </c>
       <c r="H52" s="3">
         <v>2700</v>
       </c>
       <c r="I52" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="J52" s="3">
         <v>2700</v>
       </c>
       <c r="K52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>2600</v>
       </c>
       <c r="O52" s="3">
         <v>2600</v>
@@ -4287,26 +4406,26 @@
         <v>2600</v>
       </c>
       <c r="Q52" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="R52" s="3">
         <v>2500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="S52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4331,8 +4450,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4420,71 +4542,74 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E54" s="3">
         <v>138500</v>
-      </c>
-      <c r="E54" s="3">
-        <v>151100</v>
       </c>
       <c r="F54" s="3">
         <v>151100</v>
       </c>
       <c r="G54" s="3">
+        <v>151100</v>
+      </c>
+      <c r="H54" s="3">
+        <v>157100</v>
+      </c>
+      <c r="I54" s="3">
         <v>132000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>144400</v>
       </c>
-      <c r="I54" s="3">
-        <v>166800</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>219200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>198800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>219200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>236600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>198800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>226400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>255400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>283900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>309100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>326500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>327200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>350100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>380500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4509,8 +4634,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4542,8 +4670,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4575,71 +4704,72 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E57" s="3">
         <v>8600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I57" s="3">
         <v>8800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6500</v>
       </c>
-      <c r="I57" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>7000</v>
       </c>
       <c r="N57" s="3">
         <v>7000</v>
       </c>
       <c r="O57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P57" s="3">
         <v>6500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,68 +4794,71 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J58" s="3">
         <v>4200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="M58" s="3">
         <v>4000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O58" s="3">
         <v>5600</v>
       </c>
-      <c r="L58" s="3">
-        <v>4000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>3900</v>
-      </c>
-      <c r="N58" s="3">
-        <v>5600</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>2400</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4753,71 +4886,74 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
-        <v>500</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>4200</v>
       </c>
       <c r="O59" s="3">
         <v>4200</v>
       </c>
       <c r="P59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q59" s="3">
         <v>24100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4842,71 +4978,74 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E60" s="3">
         <v>31400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>25300</v>
+      </c>
+      <c r="I60" s="3">
         <v>27800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>26100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
+        <v>37200</v>
+      </c>
+      <c r="L60" s="3">
+        <v>33400</v>
+      </c>
+      <c r="M60" s="3">
+        <v>37200</v>
+      </c>
+      <c r="N60" s="3">
+        <v>31100</v>
+      </c>
+      <c r="O60" s="3">
+        <v>33400</v>
+      </c>
+      <c r="P60" s="3">
+        <v>33500</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>32400</v>
+      </c>
+      <c r="R60" s="3">
         <v>28000</v>
       </c>
-      <c r="J60" s="3">
-        <v>37200</v>
-      </c>
-      <c r="K60" s="3">
-        <v>33400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>37200</v>
-      </c>
-      <c r="M60" s="3">
-        <v>31100</v>
-      </c>
-      <c r="N60" s="3">
-        <v>33400</v>
-      </c>
-      <c r="O60" s="3">
-        <v>33500</v>
-      </c>
-      <c r="P60" s="3">
-        <v>32400</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>28000</v>
-      </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26400</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4931,50 +5070,53 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>29300</v>
+        <v>28500</v>
       </c>
       <c r="E61" s="3">
         <v>29300</v>
       </c>
       <c r="F61" s="3">
+        <v>29300</v>
+      </c>
+      <c r="G61" s="3">
         <v>29600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I61" s="3">
         <v>25300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>25600</v>
       </c>
-      <c r="I61" s="3">
-        <v>26000</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4991,11 +5133,11 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>2100</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -5020,8 +5162,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5032,59 +5177,59 @@
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>31000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>35000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>31400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>33200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,8 +5254,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5198,8 +5346,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5287,8 +5438,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5376,71 +5530,74 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E66" s="3">
         <v>60700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>58000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>49400</v>
+      </c>
+      <c r="I66" s="3">
         <v>53100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>51700</v>
       </c>
-      <c r="I66" s="3">
-        <v>54100</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>65900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>62100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>65900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>59300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>62100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>63700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>63000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>53100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>40100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5465,8 +5622,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5498,8 +5658,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5587,8 +5748,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5676,8 +5840,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5765,8 +5932,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5854,71 +6024,74 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-824000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-797800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-776600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-761200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>-742700</v>
+      </c>
+      <c r="I72" s="3">
         <v>-730000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-711400</v>
       </c>
-      <c r="I72" s="3">
-        <v>-686600</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-635300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-577800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-635300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-604800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-577800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-546600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-511800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-477500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-443300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-415200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-385000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-351000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-324600</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5943,8 +6116,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6032,8 +6208,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6121,8 +6300,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6210,71 +6392,74 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E76" s="3">
         <v>77700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>89700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>93100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>107800</v>
+      </c>
+      <c r="I76" s="3">
         <v>78900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>92600</v>
       </c>
-      <c r="I76" s="3">
-        <v>112700</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>153300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>136700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>153300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>177300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>136700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>162700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>192000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>220900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>249900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>273400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>298800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>322400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>340500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6299,8 +6484,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6388,91 +6576,94 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
-        <v>45473</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6482,86 +6673,89 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-18600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-24900</v>
       </c>
-      <c r="I81" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-30500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-28100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-30200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-33900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-26400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-72500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-20700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-81500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6571,8 +6765,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6604,64 +6801,65 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F83" s="3">
         <v>2200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2000</v>
       </c>
       <c r="G83" s="3">
         <v>1500</v>
       </c>
       <c r="H83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L83" s="3">
+        <v>700</v>
+      </c>
+      <c r="M83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="J83" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="S83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="T83" s="3">
         <v>2100</v>
       </c>
-      <c r="P83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="R83" s="3">
-        <v>2000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>2100</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1900</v>
-      </c>
-      <c r="U83" s="3">
-        <v>700</v>
       </c>
       <c r="V83" s="3">
         <v>700</v>
@@ -6670,22 +6868,22 @@
         <v>700</v>
       </c>
       <c r="X83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y83" s="3">
         <v>2700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>500</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -6693,8 +6891,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6782,8 +6983,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6871,8 +7075,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6960,8 +7167,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7049,8 +7259,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7138,86 +7351,89 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="I89" s="3">
         <v>-17800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-16500</v>
       </c>
-      <c r="I89" s="3">
-        <v>-20800</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-24800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-27600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-24800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-26600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-27800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-23400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-26700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-19300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-26300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-16500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-20400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-61900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-17200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-15800</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7227,8 +7443,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7260,88 +7479,89 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-900</v>
       </c>
-      <c r="V91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7349,8 +7569,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7438,8 +7661,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7527,88 +7753,91 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E94" s="3">
         <v>4800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="I94" s="3">
         <v>15100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>20100</v>
       </c>
-      <c r="I94" s="3">
-        <v>30600</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-38800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>83800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>50200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>54800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>22600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-93700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>9200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-196400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>29600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>34400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -7616,8 +7845,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7649,8 +7881,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7690,8 +7923,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7738,8 +7971,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7827,8 +8063,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7916,8 +8155,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8005,43 +8247,46 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E100" s="3">
         <v>5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
-        <v>100</v>
-      </c>
       <c r="H100" s="3">
-        <v>100</v>
+        <v>37700</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
       </c>
       <c r="J100" s="3">
+        <v>100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>62100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>100</v>
       </c>
       <c r="O100" s="3">
         <v>100</v>
@@ -8050,40 +8295,40 @@
         <v>100</v>
       </c>
       <c r="Q100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R100" s="3">
         <v>200</v>
       </c>
       <c r="S100" s="3">
+        <v>200</v>
+      </c>
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>169900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>170500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8900</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
+      <c r="AB100" s="3">
+        <v>0</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
@@ -8094,88 +8339,91 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
         <v>200</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>800</v>
       </c>
       <c r="G101" s="3">
         <v>-100</v>
       </c>
       <c r="H101" s="3">
+        <v>800</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
+        <v>500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>300</v>
+      </c>
+      <c r="M101" s="3">
+        <v>200</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>200</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="V101" s="3">
+        <v>200</v>
+      </c>
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
-        <v>200</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>500</v>
-      </c>
-      <c r="U101" s="3">
-        <v>200</v>
-      </c>
-      <c r="V101" s="3">
-        <v>300</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-400</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -8183,86 +8431,89 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3900</v>
       </c>
-      <c r="I102" s="3">
-        <v>9800</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-79100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-79100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>57500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>22600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>30500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-115900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-42700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>149100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-22700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-14400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>17800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-18100</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8270,6 +8521,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
